--- a/test/tests/tests.xlsx
+++ b/test/tests/tests.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="35">
   <si>
     <t>inputs</t>
   </si>
@@ -38,6 +38,15 @@
     <t>neuron 2</t>
   </si>
   <si>
+    <t>outputs</t>
+  </si>
+  <si>
+    <t>output 1</t>
+  </si>
+  <si>
+    <t>neuron 11</t>
+  </si>
+  <si>
     <t>layer 1</t>
   </si>
   <si>
@@ -101,13 +110,13 @@
     <t>layer 3</t>
   </si>
   <si>
-    <t>neuron 11</t>
-  </si>
-  <si>
     <t>w4</t>
   </si>
   <si>
     <t>w5</t>
+  </si>
+  <si>
+    <t>output 2</t>
   </si>
   <si>
     <t>neuron 12</t>
@@ -1295,7 +1304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G64"/>
+  <dimension ref="A3:G67"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="8.88888888888889" style="1"/>
@@ -1373,802 +1382,831 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D9" s="2">
+        <f t="shared" ref="D9:G9" si="0">D59</f>
+        <v>358.103470734109</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>4.40479258242874</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>209.550660259646</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>64.5522445946282</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="6">
-        <f>IF($C10="identity",D11,IF($C10="sigmoid",1/(1+EXP(-D11)),IF($C10="tanh",(EXP(D11)-EXP(-D11))/(EXP(D11)+EXP(-D11)),IF($C10="softplus",LN(1+EXP(D11)),IF($C10="gaussian",EXP(-POWER(D11,2)),0)))))</f>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6">
+        <f>IF($C13="identity",D14,IF($C13="sigmoid",1/(1+EXP(-D14)),IF($C13="tanh",(EXP(D14)-EXP(-D14))/(EXP(D14)+EXP(-D14)),IF($C13="softplus",LN(1+EXP(D14)),IF($C13="gaussian",EXP(-POWER(D14,2)),0)))))</f>
         <v>-4.77</v>
       </c>
-      <c r="E10" s="6">
-        <f>IF($C10="identity",E11,IF($C10="sigmoid",1/(1+EXP(-E11)),IF($C10="tanh",(EXP(E11)-EXP(-E11))/(EXP(E11)+EXP(-E11)),IF($C10="softplus",LN(1+EXP(E11)),IF($C10="gaussian",EXP(-POWER(E11,2)),0)))))</f>
+      <c r="E13" s="6">
+        <f>IF($C13="identity",E14,IF($C13="sigmoid",1/(1+EXP(-E14)),IF($C13="tanh",(EXP(E14)-EXP(-E14))/(EXP(E14)+EXP(-E14)),IF($C13="softplus",LN(1+EXP(E14)),IF($C13="gaussian",EXP(-POWER(E14,2)),0)))))</f>
         <v>-5.023</v>
       </c>
-      <c r="F10" s="6">
-        <f>IF($C10="identity",F11,IF($C10="sigmoid",1/(1+EXP(-F11)),IF($C10="tanh",(EXP(F11)-EXP(-F11))/(EXP(F11)+EXP(-F11)),IF($C10="softplus",LN(1+EXP(F11)),IF($C10="gaussian",EXP(-POWER(F11,2)),0)))))</f>
+      <c r="F13" s="6">
+        <f>IF($C13="identity",F14,IF($C13="sigmoid",1/(1+EXP(-F14)),IF($C13="tanh",(EXP(F14)-EXP(-F14))/(EXP(F14)+EXP(-F14)),IF($C13="softplus",LN(1+EXP(F14)),IF($C13="gaussian",EXP(-POWER(F14,2)),0)))))</f>
         <v>-5</v>
       </c>
-      <c r="G10" s="6">
-        <f>IF($C10="identity",G11,IF($C10="sigmoid",1/(1+EXP(-G11)),IF($C10="tanh",(EXP(G11)-EXP(-G11))/(EXP(G11)+EXP(-G11)),IF($C10="softplus",LN(1+EXP(G11)),IF($C10="gaussian",EXP(-POWER(G11,2)),0)))))</f>
+      <c r="G13" s="6">
+        <f>IF($C13="identity",G14,IF($C13="sigmoid",1/(1+EXP(-G14)),IF($C13="tanh",(EXP(G14)-EXP(-G14))/(EXP(G14)+EXP(-G14)),IF($C13="softplus",LN(1+EXP(G14)),IF($C13="gaussian",EXP(-POWER(G14,2)),0)))))</f>
         <v>-5.23</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>0</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1">
         <v>-5</v>
       </c>
-      <c r="D11" s="2">
-        <f>$C12*D$4+$C11</f>
+      <c r="D14" s="2">
+        <f>$C15*D$4+$C14</f>
         <v>-4.77</v>
       </c>
-      <c r="E11" s="2">
-        <f>$C12*E$4+$C11</f>
+      <c r="E14" s="2">
+        <f>$C15*E$4+$C14</f>
         <v>-5.023</v>
       </c>
-      <c r="F11" s="2">
-        <f>$C12*F$4+$C11</f>
+      <c r="F14" s="2">
+        <f>$C15*F$4+$C14</f>
         <v>-5</v>
       </c>
-      <c r="G11" s="2">
-        <f>$C12*G$4+$C11</f>
+      <c r="G14" s="2">
+        <f>$C15*G$4+$C14</f>
         <v>-5.23</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6">
+        <f>IF($C17="identity",D18,IF($C17="sigmoid",1/(1+EXP(-D18)),IF($C17="tanh",(EXP(D18)-EXP(-D18))/(EXP(D18)+EXP(-D18)),IF($C17="softplus",LN(1+EXP(D18)),IF($C17="gaussian",EXP(-POWER(D18,2)),0)))))</f>
+        <v>-68.4</v>
+      </c>
+      <c r="E17" s="6">
+        <f>IF($C17="identity",E18,IF($C17="sigmoid",1/(1+EXP(-E18)),IF($C17="tanh",(EXP(E18)-EXP(-E18))/(EXP(E18)+EXP(-E18)),IF($C17="softplus",LN(1+EXP(E18)),IF($C17="gaussian",EXP(-POWER(E18,2)),0)))))</f>
+        <v>1.29</v>
+      </c>
+      <c r="F17" s="6">
+        <f>IF($C17="identity",F18,IF($C17="sigmoid",1/(1+EXP(-F18)),IF($C17="tanh",(EXP(F18)-EXP(-F18))/(EXP(F18)+EXP(-F18)),IF($C17="softplus",LN(1+EXP(F18)),IF($C17="gaussian",EXP(-POWER(F18,2)),0)))))</f>
+        <v>-40.8</v>
+      </c>
+      <c r="G17" s="6">
+        <f>IF($C17="identity",G18,IF($C17="sigmoid",1/(1+EXP(-G18)),IF($C17="tanh",(EXP(G18)-EXP(-G18))/(EXP(G18)+EXP(-G18)),IF($C17="softplus",LN(1+EXP(G18)),IF($C17="gaussian",EXP(-POWER(G18,2)),0)))))</f>
+        <v>-13.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="D18" s="2">
+        <f>$C19*D$5+$C18</f>
+        <v>-68.4</v>
+      </c>
+      <c r="E18" s="2">
+        <f>$C19*E$5+$C18</f>
+        <v>1.29</v>
+      </c>
+      <c r="F18" s="2">
+        <f>$C19*F$5+$C18</f>
+        <v>-40.8</v>
+      </c>
+      <c r="G18" s="2">
+        <f>$C19*G$5+$C18</f>
+        <v>-13.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="6">
+        <f>IF($C21="identity",D22,IF($C21="sigmoid",1/(1+EXP(-D22)),IF($C21="tanh",(EXP(D22)-EXP(-D22))/(EXP(D22)+EXP(-D22)),IF($C21="softplus",LN(1+EXP(D22)),IF($C21="gaussian",EXP(-POWER(D22,2)),0)))))</f>
+        <v>0.635</v>
+      </c>
+      <c r="E21" s="6">
+        <f>IF($C21="identity",E22,IF($C21="sigmoid",1/(1+EXP(-E22)),IF($C21="tanh",(EXP(E22)-EXP(-E22))/(EXP(E22)+EXP(-E22)),IF($C21="softplus",LN(1+EXP(E22)),IF($C21="gaussian",EXP(-POWER(E22,2)),0)))))</f>
+        <v>-2.794</v>
+      </c>
+      <c r="F21" s="6">
+        <f>IF($C21="identity",F22,IF($C21="sigmoid",1/(1+EXP(-F22)),IF($C21="tanh",(EXP(F22)-EXP(-F22))/(EXP(F22)+EXP(-F22)),IF($C21="softplus",LN(1+EXP(F22)),IF($C21="gaussian",EXP(-POWER(F22,2)),0)))))</f>
+        <v>12.7</v>
+      </c>
+      <c r="G21" s="6">
+        <f>IF($C21="identity",G22,IF($C21="sigmoid",1/(1+EXP(-G22)),IF($C21="tanh",(EXP(G22)-EXP(-G22))/(EXP(G22)+EXP(-G22)),IF($C21="softplus",LN(1+EXP(G22)),IF($C21="gaussian",EXP(-POWER(G22,2)),0)))))</f>
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <f>$C23*D$6+$C22</f>
+        <v>0.635</v>
+      </c>
+      <c r="E22" s="2">
+        <f>$C23*E$6+$C22</f>
+        <v>-2.794</v>
+      </c>
+      <c r="F22" s="2">
+        <f>$C23*F$6+$C22</f>
+        <v>12.7</v>
+      </c>
+      <c r="G22" s="2">
+        <f>$C23*G$6+$C22</f>
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="6">
+        <f>IF($C27="identity",D28,IF($C27="sigmoid",1/(1+EXP(-D28)),IF($C27="tanh",(EXP(D28)-EXP(-D28))/(EXP(D28)+EXP(-D28)),IF($C27="softplus",LN(1+EXP(D28)),IF($C27="gaussian",EXP(-POWER(D28,2)),0)))))</f>
+        <v>-84.8116</v>
+      </c>
+      <c r="E27" s="6">
+        <f>IF($C27="identity",E28,IF($C27="sigmoid",1/(1+EXP(-E28)),IF($C27="tanh",(EXP(E28)-EXP(-E28))/(EXP(E28)+EXP(-E28)),IF($C27="softplus",LN(1+EXP(E28)),IF($C27="gaussian",EXP(-POWER(E28,2)),0)))))</f>
+        <v>-19.41549</v>
+      </c>
+      <c r="F27" s="6">
+        <f>IF($C27="identity",F28,IF($C27="sigmoid",1/(1+EXP(-F28)),IF($C27="tanh",(EXP(F28)-EXP(-F28))/(EXP(F28)+EXP(-F28)),IF($C27="softplus",LN(1+EXP(F28)),IF($C27="gaussian",EXP(-POWER(F28,2)),0)))))</f>
+        <v>12.2</v>
+      </c>
+      <c r="G27" s="6">
+        <f>IF($C27="identity",G28,IF($C27="sigmoid",1/(1+EXP(-G28)),IF($C27="tanh",(EXP(G28)-EXP(-G28))/(EXP(G28)+EXP(-G28)),IF($C27="softplus",LN(1+EXP(G28)),IF($C27="gaussian",EXP(-POWER(G28,2)),0)))))</f>
+        <v>-35.5049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="1">
+        <v>-5</v>
+      </c>
+      <c r="D28" s="2">
+        <f>$C29*D$13+$C30*D$17+$C31*D$21+$C28</f>
+        <v>-84.8116</v>
+      </c>
+      <c r="E28" s="2">
+        <f>$C29*E$13+$C30*E$17+$C31*E$21+$C28</f>
+        <v>-19.41549</v>
+      </c>
+      <c r="F28" s="2">
+        <f>$C29*F$13+$C30*F$17+$C31*F$21+$C28</f>
+        <v>12.2</v>
+      </c>
+      <c r="G28" s="2">
+        <f>$C29*G$13+$C30*G$17+$C31*G$21+$C28</f>
+        <v>-35.5049</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>8</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="1">
         <v>0.23</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="5" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="B30" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>10</v>
       </c>
-      <c r="D14" s="6">
-        <f>IF($C14="identity",D15,IF($C14="sigmoid",1/(1+EXP(-D15)),IF($C14="tanh",(EXP(D15)-EXP(-D15))/(EXP(D15)+EXP(-D15)),IF($C14="softplus",LN(1+EXP(D15)),IF($C14="gaussian",EXP(-POWER(D15,2)),0)))))</f>
-        <v>-68.4</v>
-      </c>
-      <c r="E14" s="6">
-        <f>IF($C14="identity",E15,IF($C14="sigmoid",1/(1+EXP(-E15)),IF($C14="tanh",(EXP(E15)-EXP(-E15))/(EXP(E15)+EXP(-E15)),IF($C14="softplus",LN(1+EXP(E15)),IF($C14="gaussian",EXP(-POWER(E15,2)),0)))))</f>
-        <v>1.29</v>
-      </c>
-      <c r="F14" s="6">
-        <f>IF($C14="identity",F15,IF($C14="sigmoid",1/(1+EXP(-F15)),IF($C14="tanh",(EXP(F15)-EXP(-F15))/(EXP(F15)+EXP(-F15)),IF($C14="softplus",LN(1+EXP(F15)),IF($C14="gaussian",EXP(-POWER(F15,2)),0)))))</f>
-        <v>-40.8</v>
-      </c>
-      <c r="G14" s="6">
-        <f>IF($C14="identity",G15,IF($C14="sigmoid",1/(1+EXP(-G15)),IF($C14="tanh",(EXP(G15)-EXP(-G15))/(EXP(G15)+EXP(-G15)),IF($C14="softplus",LN(1+EXP(G15)),IF($C14="gaussian",EXP(-POWER(G15,2)),0)))))</f>
-        <v>-13.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="D15" s="2">
-        <f>$C16*D$5+$C15</f>
-        <v>-68.4</v>
-      </c>
-      <c r="E15" s="2">
-        <f>$C16*E$5+$C15</f>
-        <v>1.29</v>
-      </c>
-      <c r="F15" s="2">
-        <f>$C16*F$5+$C15</f>
-        <v>-40.8</v>
-      </c>
-      <c r="G15" s="2">
-        <f>$C16*G$5+$C15</f>
-        <v>-13.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="1">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6">
-        <f>IF($C18="identity",D19,IF($C18="sigmoid",1/(1+EXP(-D19)),IF($C18="tanh",(EXP(D19)-EXP(-D19))/(EXP(D19)+EXP(-D19)),IF($C18="softplus",LN(1+EXP(D19)),IF($C18="gaussian",EXP(-POWER(D19,2)),0)))))</f>
-        <v>0.635</v>
-      </c>
-      <c r="E18" s="6">
-        <f>IF($C18="identity",E19,IF($C18="sigmoid",1/(1+EXP(-E19)),IF($C18="tanh",(EXP(E19)-EXP(-E19))/(EXP(E19)+EXP(-E19)),IF($C18="softplus",LN(1+EXP(E19)),IF($C18="gaussian",EXP(-POWER(E19,2)),0)))))</f>
-        <v>-2.794</v>
-      </c>
-      <c r="F18" s="6">
-        <f>IF($C18="identity",F19,IF($C18="sigmoid",1/(1+EXP(-F19)),IF($C18="tanh",(EXP(F19)-EXP(-F19))/(EXP(F19)+EXP(-F19)),IF($C18="softplus",LN(1+EXP(F19)),IF($C18="gaussian",EXP(-POWER(F19,2)),0)))))</f>
-        <v>12.7</v>
-      </c>
-      <c r="G18" s="6">
-        <f>IF($C18="identity",G19,IF($C18="sigmoid",1/(1+EXP(-G19)),IF($C18="tanh",(EXP(G19)-EXP(-G19))/(EXP(G19)+EXP(-G19)),IF($C18="softplus",LN(1+EXP(G19)),IF($C18="gaussian",EXP(-POWER(G19,2)),0)))))</f>
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>4</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2">
-        <f>$C20*D$6+$C19</f>
-        <v>0.635</v>
-      </c>
-      <c r="E19" s="2">
-        <f>$C20*E$6+$C19</f>
-        <v>-2.794</v>
-      </c>
-      <c r="F19" s="2">
-        <f>$C20*F$6+$C19</f>
-        <v>12.7</v>
-      </c>
-      <c r="G19" s="2">
-        <f>$C20*G$6+$C19</f>
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>5</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>6</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6">
-        <f>IF($C24="identity",D25,IF($C24="sigmoid",1/(1+EXP(-D25)),IF($C24="tanh",(EXP(D25)-EXP(-D25))/(EXP(D25)+EXP(-D25)),IF($C24="softplus",LN(1+EXP(D25)),IF($C24="gaussian",EXP(-POWER(D25,2)),0)))))</f>
-        <v>-84.8116</v>
-      </c>
-      <c r="E24" s="6">
-        <f>IF($C24="identity",E25,IF($C24="sigmoid",1/(1+EXP(-E25)),IF($C24="tanh",(EXP(E25)-EXP(-E25))/(EXP(E25)+EXP(-E25)),IF($C24="softplus",LN(1+EXP(E25)),IF($C24="gaussian",EXP(-POWER(E25,2)),0)))))</f>
-        <v>-19.41549</v>
-      </c>
-      <c r="F24" s="6">
-        <f>IF($C24="identity",F25,IF($C24="sigmoid",1/(1+EXP(-F25)),IF($C24="tanh",(EXP(F25)-EXP(-F25))/(EXP(F25)+EXP(-F25)),IF($C24="softplus",LN(1+EXP(F25)),IF($C24="gaussian",EXP(-POWER(F25,2)),0)))))</f>
-        <v>12.2</v>
-      </c>
-      <c r="G24" s="6">
-        <f>IF($C24="identity",G25,IF($C24="sigmoid",1/(1+EXP(-G25)),IF($C24="tanh",(EXP(G25)-EXP(-G25))/(EXP(G25)+EXP(-G25)),IF($C24="softplus",LN(1+EXP(G25)),IF($C24="gaussian",EXP(-POWER(G25,2)),0)))))</f>
-        <v>-35.5049</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>7</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="1">
-        <v>-5</v>
-      </c>
-      <c r="D25" s="2">
-        <f>$C26*D$10+$C27*D$14+$C28*D$18+$C25</f>
-        <v>-84.8116</v>
-      </c>
-      <c r="E25" s="2">
-        <f>$C26*E$10+$C27*E$14+$C28*E$18+$C25</f>
-        <v>-19.41549</v>
-      </c>
-      <c r="F25" s="2">
-        <f>$C26*F$10+$C27*F$14+$C28*F$18+$C25</f>
-        <v>12.2</v>
-      </c>
-      <c r="G25" s="2">
-        <f>$C26*G$10+$C27*G$14+$C28*G$18+$C25</f>
-        <v>-35.5049</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>8</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>9</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>10</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>11</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="6">
-        <f>IF($C30="identity",D31,IF($C30="sigmoid",1/(1+EXP(-D31)),IF($C30="tanh",(EXP(D31)-EXP(-D31))/(EXP(D31)+EXP(-D31)),IF($C30="softplus",LN(1+EXP(D31)),IF($C30="gaussian",EXP(-POWER(D31,2)),0)))))</f>
-        <v>319.4958</v>
-      </c>
-      <c r="E30" s="6">
-        <f>IF($C30="identity",E31,IF($C30="sigmoid",1/(1+EXP(-E31)),IF($C30="tanh",(EXP(E31)-EXP(-E31))/(EXP(E31)+EXP(-E31)),IF($C30="softplus",LN(1+EXP(E31)),IF($C30="gaussian",EXP(-POWER(E31,2)),0)))))</f>
-        <v>2.45106540760707</v>
-      </c>
-      <c r="F30" s="6">
-        <f>IF($C30="identity",F31,IF($C30="sigmoid",1/(1+EXP(-F31)),IF($C30="tanh",(EXP(F31)-EXP(-F31))/(EXP(F31)+EXP(-F31)),IF($C30="softplus",LN(1+EXP(F31)),IF($C30="gaussian",EXP(-POWER(F31,2)),0)))))</f>
-        <v>180.48</v>
-      </c>
-      <c r="G30" s="6">
-        <f>IF($C30="identity",G31,IF($C30="sigmoid",1/(1+EXP(-G31)),IF($C30="tanh",(EXP(G31)-EXP(-G31))/(EXP(G31)+EXP(-G31)),IF($C30="softplus",LN(1+EXP(G31)),IF($C30="gaussian",EXP(-POWER(G31,2)),0)))))</f>
-        <v>68.7692</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>12</v>
-      </c>
       <c r="B31" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C31" s="1">
         <v>5.3</v>
       </c>
-      <c r="D31" s="2">
-        <f>$C32*D$10+$C33*D$14+$C34*D$18+$C31</f>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>11</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="6">
+        <f>IF($C33="identity",D34,IF($C33="sigmoid",1/(1+EXP(-D34)),IF($C33="tanh",(EXP(D34)-EXP(-D34))/(EXP(D34)+EXP(-D34)),IF($C33="softplus",LN(1+EXP(D34)),IF($C33="gaussian",EXP(-POWER(D34,2)),0)))))</f>
         <v>319.4958</v>
       </c>
-      <c r="E31" s="2">
-        <f>$C32*E$10+$C33*E$14+$C34*E$18+$C31</f>
+      <c r="E33" s="6">
+        <f>IF($C33="identity",E34,IF($C33="sigmoid",1/(1+EXP(-E34)),IF($C33="tanh",(EXP(E34)-EXP(-E34))/(EXP(E34)+EXP(-E34)),IF($C33="softplus",LN(1+EXP(E34)),IF($C33="gaussian",EXP(-POWER(E34,2)),0)))))</f>
+        <v>2.45106540760707</v>
+      </c>
+      <c r="F33" s="6">
+        <f>IF($C33="identity",F34,IF($C33="sigmoid",1/(1+EXP(-F34)),IF($C33="tanh",(EXP(F34)-EXP(-F34))/(EXP(F34)+EXP(-F34)),IF($C33="softplus",LN(1+EXP(F34)),IF($C33="gaussian",EXP(-POWER(F34,2)),0)))))</f>
+        <v>180.48</v>
+      </c>
+      <c r="G33" s="6">
+        <f>IF($C33="identity",G34,IF($C33="sigmoid",1/(1+EXP(-G34)),IF($C33="tanh",(EXP(G34)-EXP(-G34))/(EXP(G34)+EXP(-G34)),IF($C33="softplus",LN(1+EXP(G34)),IF($C33="gaussian",EXP(-POWER(G34,2)),0)))))</f>
+        <v>68.7692</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>12</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="D34" s="2">
+        <f>$C35*D$13+$C36*D$17+$C37*D$21+$C34</f>
+        <v>319.4958</v>
+      </c>
+      <c r="E34" s="2">
+        <f>$C35*E$13+$C36*E$17+$C37*E$21+$C34</f>
         <v>2.36092</v>
       </c>
-      <c r="F31" s="2">
-        <f>$C32*F$10+$C33*F$14+$C34*F$18+$C31</f>
+      <c r="F34" s="2">
+        <f>$C35*F$13+$C36*F$17+$C37*F$21+$C34</f>
         <v>180.48</v>
       </c>
-      <c r="G31" s="2">
-        <f>$C32*G$10+$C33*G$14+$C34*G$18+$C31</f>
+      <c r="G34" s="2">
+        <f>$C35*G$13+$C36*G$17+$C37*G$21+$C34</f>
         <v>68.7692</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>13</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="1">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>14</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>15</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>16</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="1">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
+      <c r="C39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="6">
+        <f>IF($C39="identity",D40,IF($C39="sigmoid",1/(1+EXP(-D40)),IF($C39="tanh",(EXP(D40)-EXP(-D40))/(EXP(D40)+EXP(-D40)),IF($C39="softplus",LN(1+EXP(D40)),IF($C39="gaussian",EXP(-POWER(D40,2)),0)))))</f>
+        <v>-1</v>
+      </c>
+      <c r="E39" s="6">
+        <f>IF($C39="identity",E40,IF($C39="sigmoid",1/(1+EXP(-E40)),IF($C39="tanh",(EXP(E40)-EXP(-E40))/(EXP(E40)+EXP(-E40)),IF($C39="softplus",LN(1+EXP(E40)),IF($C39="gaussian",EXP(-POWER(E40,2)),0)))))</f>
+        <v>0.99853483244595</v>
+      </c>
+      <c r="F39" s="6">
+        <f>IF($C39="identity",F40,IF($C39="sigmoid",1/(1+EXP(-F40)),IF($C39="tanh",(EXP(F40)-EXP(-F40))/(EXP(F40)+EXP(-F40)),IF($C39="softplus",LN(1+EXP(F40)),IF($C39="gaussian",EXP(-POWER(F40,2)),0)))))</f>
+        <v>-1</v>
+      </c>
+      <c r="G39" s="6">
+        <f>IF($C39="identity",G40,IF($C39="sigmoid",1/(1+EXP(-G40)),IF($C39="tanh",(EXP(G40)-EXP(-G40))/(EXP(G40)+EXP(-G40)),IF($C39="softplus",LN(1+EXP(G40)),IF($C39="gaussian",EXP(-POWER(G40,2)),0)))))</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>17</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="1">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34">
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <f>$C41*D$13+$C42*D$17+$C43*D$21+$C40</f>
+        <v>-618.158</v>
+      </c>
+      <c r="E40" s="2">
+        <f>$C41*E$13+$C42*E$17+$C43*E$21+$C40</f>
+        <v>3.6091</v>
+      </c>
+      <c r="F40" s="2">
+        <f>$C41*F$13+$C42*F$17+$C43*F$21+$C40</f>
+        <v>-380.24</v>
+      </c>
+      <c r="G40" s="2">
+        <f>$C41*G$13+$C42*G$17+$C43*G$21+$C40</f>
+        <v>-125.939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>18</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="4" t="s">
+      <c r="C41" s="1">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>19</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>20</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>16</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="C43" s="1">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="6">
+        <f>IF($C45="identity",D46,IF($C45="sigmoid",1/(1+EXP(-D46)),IF($C45="tanh",(EXP(D46)-EXP(-D46))/(EXP(D46)+EXP(-D46)),IF($C45="softplus",LN(1+EXP(D46)),IF($C45="gaussian",EXP(-POWER(D46,2)),0)))))</f>
+        <v>0.204785304533942</v>
+      </c>
+      <c r="E45" s="6">
+        <f>IF($C45="identity",E46,IF($C45="sigmoid",1/(1+EXP(-E46)),IF($C45="tanh",(EXP(E46)-EXP(-E46))/(EXP(E46)+EXP(-E46)),IF($C45="softplus",LN(1+EXP(E46)),IF($C45="gaussian",EXP(-POWER(E46,2)),0)))))</f>
+        <v>0.482944120098951</v>
+      </c>
+      <c r="F45" s="6">
+        <f>IF($C45="identity",F46,IF($C45="sigmoid",1/(1+EXP(-F46)),IF($C45="tanh",(EXP(F46)-EXP(-F46))/(EXP(F46)+EXP(-F46)),IF($C45="softplus",LN(1+EXP(F46)),IF($C45="gaussian",EXP(-POWER(F46,2)),0)))))</f>
+        <v>0.390550216371675</v>
+      </c>
+      <c r="G45" s="6">
+        <f>IF($C45="identity",G46,IF($C45="sigmoid",1/(1+EXP(-G46)),IF($C45="tanh",(EXP(G46)-EXP(-G46))/(EXP(G46)+EXP(-G46)),IF($C45="softplus",LN(1+EXP(G46)),IF($C45="gaussian",EXP(-POWER(G46,2)),0)))))</f>
+        <v>0.412776309160665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>22</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D46" s="2">
+        <f>$C47*D$13+$C48*D$17+$C49*D$21+$C46</f>
+        <v>-1.35665</v>
+      </c>
+      <c r="E46" s="2">
+        <f>$C47*E$13+$C48*E$17+$C49*E$21+$C46</f>
+        <v>-0.06825</v>
+      </c>
+      <c r="F46" s="2">
+        <f>$C47*F$13+$C48*F$17+$C49*F$21+$C46</f>
+        <v>-0.445</v>
+      </c>
+      <c r="G46" s="2">
+        <f>$C47*G$13+$C48*G$17+$C49*G$21+$C46</f>
+        <v>-0.3525</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>23</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>24</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>25</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>26</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="6">
+        <f>IF($C51="identity",D52,IF($C51="sigmoid",1/(1+EXP(-D52)),IF($C51="tanh",(EXP(D52)-EXP(-D52))/(EXP(D52)+EXP(-D52)),IF($C51="softplus",LN(1+EXP(D52)),IF($C51="gaussian",EXP(-POWER(D52,2)),0)))))</f>
+        <v>0.805554031824201</v>
+      </c>
+      <c r="E51" s="6">
+        <f>IF($C51="identity",E52,IF($C51="sigmoid",1/(1+EXP(-E52)),IF($C51="tanh",(EXP(E52)-EXP(-E52))/(EXP(E52)+EXP(-E52)),IF($C51="softplus",LN(1+EXP(E52)),IF($C51="gaussian",EXP(-POWER(E52,2)),0)))))</f>
+        <v>0.954209290041129</v>
+      </c>
+      <c r="F51" s="6">
+        <f>IF($C51="identity",F52,IF($C51="sigmoid",1/(1+EXP(-F52)),IF($C51="tanh",(EXP(F52)-EXP(-F52))/(EXP(F52)+EXP(-F52)),IF($C51="softplus",LN(1+EXP(F52)),IF($C51="gaussian",EXP(-POWER(F52,2)),0)))))</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="6">
+        <f>IF($C51="identity",G52,IF($C51="sigmoid",1/(1+EXP(-G52)),IF($C51="tanh",(EXP(G52)-EXP(-G52))/(EXP(G52)+EXP(-G52)),IF($C51="softplus",LN(1+EXP(G52)),IF($C51="gaussian",EXP(-POWER(G52,2)),0)))))</f>
+        <v>4.4595186622541e-9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>27</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="1">
+        <v>25</v>
+      </c>
+      <c r="D52" s="2">
+        <f>$C53*D$13+$C54*D$17+$C55*D$21+$C52</f>
+        <v>-0.465000000000003</v>
+      </c>
+      <c r="E52" s="2">
+        <f>$C53*E$13+$C54*E$17+$C55*E$21+$C52</f>
+        <v>0.216499999999996</v>
+      </c>
+      <c r="F52" s="2">
+        <f>$C53*F$13+$C54*F$17+$C55*F$21+$C52</f>
+        <v>134.1</v>
+      </c>
+      <c r="G52" s="2">
+        <f>$C53*G$13+$C54*G$17+$C55*G$21+$C52</f>
+        <v>-4.385</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>28</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="1">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>29</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>30</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="8"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="6">
-        <f>IF($C36="identity",D37,IF($C36="sigmoid",1/(1+EXP(-D37)),IF($C36="tanh",(EXP(D37)-EXP(-D37))/(EXP(D37)+EXP(-D37)),IF($C36="softplus",LN(1+EXP(D37)),IF($C36="gaussian",EXP(-POWER(D37,2)),0)))))</f>
-        <v>-1</v>
-      </c>
-      <c r="E36" s="6">
-        <f>IF($C36="identity",E37,IF($C36="sigmoid",1/(1+EXP(-E37)),IF($C36="tanh",(EXP(E37)-EXP(-E37))/(EXP(E37)+EXP(-E37)),IF($C36="softplus",LN(1+EXP(E37)),IF($C36="gaussian",EXP(-POWER(E37,2)),0)))))</f>
-        <v>0.99853483244595</v>
-      </c>
-      <c r="F36" s="6">
-        <f>IF($C36="identity",F37,IF($C36="sigmoid",1/(1+EXP(-F37)),IF($C36="tanh",(EXP(F37)-EXP(-F37))/(EXP(F37)+EXP(-F37)),IF($C36="softplus",LN(1+EXP(F37)),IF($C36="gaussian",EXP(-POWER(F37,2)),0)))))</f>
-        <v>-1</v>
-      </c>
-      <c r="G36" s="6">
-        <f>IF($C36="identity",G37,IF($C36="sigmoid",1/(1+EXP(-G37)),IF($C36="tanh",(EXP(G37)-EXP(-G37))/(EXP(G37)+EXP(-G37)),IF($C36="softplus",LN(1+EXP(G37)),IF($C36="gaussian",EXP(-POWER(G37,2)),0)))))</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>17</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <f>$C38*D$10+$C39*D$14+$C40*D$18+$C37</f>
-        <v>-618.158</v>
-      </c>
-      <c r="E37" s="2">
-        <f>$C38*E$10+$C39*E$14+$C40*E$18+$C37</f>
-        <v>3.6091</v>
-      </c>
-      <c r="F37" s="2">
-        <f>$C38*F$10+$C39*F$14+$C40*F$18+$C37</f>
-        <v>-380.24</v>
-      </c>
-      <c r="G37" s="2">
-        <f>$C38*G$10+$C39*G$14+$C40*G$18+$C37</f>
-        <v>-125.939</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38">
-        <v>18</v>
-      </c>
-      <c r="B38" s="7" t="s">
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>31</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="1">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
-        <v>19</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="1">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>20</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="1">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="6">
-        <f>IF($C42="identity",D43,IF($C42="sigmoid",1/(1+EXP(-D43)),IF($C42="tanh",(EXP(D43)-EXP(-D43))/(EXP(D43)+EXP(-D43)),IF($C42="softplus",LN(1+EXP(D43)),IF($C42="gaussian",EXP(-POWER(D43,2)),0)))))</f>
-        <v>0.204785304533942</v>
-      </c>
-      <c r="E42" s="6">
-        <f>IF($C42="identity",E43,IF($C42="sigmoid",1/(1+EXP(-E43)),IF($C42="tanh",(EXP(E43)-EXP(-E43))/(EXP(E43)+EXP(-E43)),IF($C42="softplus",LN(1+EXP(E43)),IF($C42="gaussian",EXP(-POWER(E43,2)),0)))))</f>
-        <v>0.482944120098951</v>
-      </c>
-      <c r="F42" s="6">
-        <f>IF($C42="identity",F43,IF($C42="sigmoid",1/(1+EXP(-F43)),IF($C42="tanh",(EXP(F43)-EXP(-F43))/(EXP(F43)+EXP(-F43)),IF($C42="softplus",LN(1+EXP(F43)),IF($C42="gaussian",EXP(-POWER(F43,2)),0)))))</f>
-        <v>0.390550216371675</v>
-      </c>
-      <c r="G42" s="6">
-        <f>IF($C42="identity",G43,IF($C42="sigmoid",1/(1+EXP(-G43)),IF($C42="tanh",(EXP(G43)-EXP(-G43))/(EXP(G43)+EXP(-G43)),IF($C42="softplus",LN(1+EXP(G43)),IF($C42="gaussian",EXP(-POWER(G43,2)),0)))))</f>
-        <v>0.412776309160665</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>22</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D43" s="2">
-        <f>$C44*D$10+$C45*D$14+$C46*D$18+$C43</f>
-        <v>-1.35665</v>
-      </c>
-      <c r="E43" s="2">
-        <f>$C44*E$10+$C45*E$14+$C46*E$18+$C43</f>
-        <v>-0.06825</v>
-      </c>
-      <c r="F43" s="2">
-        <f>$C44*F$10+$C45*F$14+$C46*F$18+$C43</f>
-        <v>-0.445</v>
-      </c>
-      <c r="G43" s="2">
-        <f>$C44*G$10+$C45*G$14+$C46*G$18+$C43</f>
-        <v>-0.3525</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44">
-        <v>23</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
-        <v>24</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
-        <v>25</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>26</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="6">
-        <f>IF($C48="identity",D49,IF($C48="sigmoid",1/(1+EXP(-D49)),IF($C48="tanh",(EXP(D49)-EXP(-D49))/(EXP(D49)+EXP(-D49)),IF($C48="softplus",LN(1+EXP(D49)),IF($C48="gaussian",EXP(-POWER(D49,2)),0)))))</f>
-        <v>0.805554031824201</v>
-      </c>
-      <c r="E48" s="6">
-        <f>IF($C48="identity",E49,IF($C48="sigmoid",1/(1+EXP(-E49)),IF($C48="tanh",(EXP(E49)-EXP(-E49))/(EXP(E49)+EXP(-E49)),IF($C48="softplus",LN(1+EXP(E49)),IF($C48="gaussian",EXP(-POWER(E49,2)),0)))))</f>
-        <v>0.954209290041129</v>
-      </c>
-      <c r="F48" s="6">
-        <f>IF($C48="identity",F49,IF($C48="sigmoid",1/(1+EXP(-F49)),IF($C48="tanh",(EXP(F49)-EXP(-F49))/(EXP(F49)+EXP(-F49)),IF($C48="softplus",LN(1+EXP(F49)),IF($C48="gaussian",EXP(-POWER(F49,2)),0)))))</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="6">
-        <f>IF($C48="identity",G49,IF($C48="sigmoid",1/(1+EXP(-G49)),IF($C48="tanh",(EXP(G49)-EXP(-G49))/(EXP(G49)+EXP(-G49)),IF($C48="softplus",LN(1+EXP(G49)),IF($C48="gaussian",EXP(-POWER(G49,2)),0)))))</f>
-        <v>4.4595186622541e-9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>27</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="1">
-        <v>25</v>
-      </c>
-      <c r="D49" s="2">
-        <f>$C50*D$10+$C51*D$14+$C52*D$18+$C49</f>
-        <v>-0.465000000000003</v>
-      </c>
-      <c r="E49" s="2">
-        <f>$C50*E$10+$C51*E$14+$C52*E$18+$C49</f>
-        <v>0.216499999999996</v>
-      </c>
-      <c r="F49" s="2">
-        <f>$C50*F$10+$C51*F$14+$C52*F$18+$C49</f>
-        <v>134.1</v>
-      </c>
-      <c r="G49" s="2">
-        <f>$C50*G$10+$C51*G$14+$C52*G$18+$C49</f>
-        <v>-4.385</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
-        <v>28</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="1">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>29</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>30</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="8"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>31</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="6">
-        <f>IF($C56="identity",D57,IF($C56="sigmoid",1/(1+EXP(-D57)),IF($C56="tanh",(EXP(D57)-EXP(-D57))/(EXP(D57)+EXP(-D57)),IF($C56="softplus",LN(1+EXP(D57)),IF($C56="gaussian",EXP(-POWER(D57,2)),0)))))</f>
+      <c r="C59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="6">
+        <f>IF($C59="identity",D60,IF($C59="sigmoid",1/(1+EXP(-D60)),IF($C59="tanh",(EXP(D60)-EXP(-D60))/(EXP(D60)+EXP(-D60)),IF($C59="softplus",LN(1+EXP(D60)),IF($C59="gaussian",EXP(-POWER(D60,2)),0)))))</f>
         <v>358.103470734109</v>
       </c>
-      <c r="E56" s="6">
-        <f>IF($C56="identity",E57,IF($C56="sigmoid",1/(1+EXP(-E57)),IF($C56="tanh",(EXP(E57)-EXP(-E57))/(EXP(E57)+EXP(-E57)),IF($C56="softplus",LN(1+EXP(E57)),IF($C56="gaussian",EXP(-POWER(E57,2)),0)))))</f>
+      <c r="E59" s="6">
+        <f>IF($C59="identity",E60,IF($C59="sigmoid",1/(1+EXP(-E60)),IF($C59="tanh",(EXP(E60)-EXP(-E60))/(EXP(E60)+EXP(-E60)),IF($C59="softplus",LN(1+EXP(E60)),IF($C59="gaussian",EXP(-POWER(E60,2)),0)))))</f>
         <v>4.40479258242874</v>
       </c>
-      <c r="F56" s="6">
-        <f>IF($C56="identity",F57,IF($C56="sigmoid",1/(1+EXP(-F57)),IF($C56="tanh",(EXP(F57)-EXP(-F57))/(EXP(F57)+EXP(-F57)),IF($C56="softplus",LN(1+EXP(F57)),IF($C56="gaussian",EXP(-POWER(F57,2)),0)))))</f>
+      <c r="F59" s="6">
+        <f>IF($C59="identity",F60,IF($C59="sigmoid",1/(1+EXP(-F60)),IF($C59="tanh",(EXP(F60)-EXP(-F60))/(EXP(F60)+EXP(-F60)),IF($C59="softplus",LN(1+EXP(F60)),IF($C59="gaussian",EXP(-POWER(F60,2)),0)))))</f>
         <v>209.550660259646</v>
       </c>
-      <c r="G56" s="6">
-        <f>IF($C56="identity",G57,IF($C56="sigmoid",1/(1+EXP(-G57)),IF($C56="tanh",(EXP(G57)-EXP(-G57))/(EXP(G57)+EXP(-G57)),IF($C56="softplus",LN(1+EXP(G57)),IF($C56="gaussian",EXP(-POWER(G57,2)),0)))))</f>
+      <c r="G59" s="6">
+        <f>IF($C59="identity",G60,IF($C59="sigmoid",1/(1+EXP(-G60)),IF($C59="tanh",(EXP(G60)-EXP(-G60))/(EXP(G60)+EXP(-G60)),IF($C59="softplus",LN(1+EXP(G60)),IF($C59="gaussian",EXP(-POWER(G60,2)),0)))))</f>
         <v>64.5522445946282</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
+    <row r="60" spans="1:7">
+      <c r="A60">
         <v>32</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="1">
+      <c r="B60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="1">
         <v>-5</v>
       </c>
-      <c r="D57" s="2">
-        <f>$C58*D$24+$C59*D$30+$C60*D$36+$C61*D$42+$C62*D$48+$C57</f>
+      <c r="D60" s="2">
+        <f>$C61*D$27+$C62*D$33+$C63*D$39+$C64*D$45+$C65*D$51+$C60</f>
         <v>358.103470734109</v>
       </c>
-      <c r="E57" s="2">
-        <f>$C58*E$24+$C59*E$30+$C60*E$36+$C61*E$42+$C62*E$48+$C57</f>
+      <c r="E60" s="2">
+        <f>$C61*E$27+$C62*E$33+$C63*E$39+$C64*E$45+$C65*E$51+$C60</f>
         <v>4.40479258242874</v>
       </c>
-      <c r="F57" s="2">
-        <f>$C58*F$24+$C59*F$30+$C60*F$36+$C61*F$42+$C62*F$48+$C57</f>
+      <c r="F60" s="2">
+        <f>$C61*F$27+$C62*F$33+$C63*F$39+$C64*F$45+$C65*F$51+$C60</f>
         <v>209.550660259646</v>
       </c>
-      <c r="G57" s="2">
-        <f>$C58*G$24+$C59*G$30+$C60*G$36+$C61*G$42+$C62*G$48+$C57</f>
+      <c r="G60" s="2">
+        <f>$C61*G$27+$C62*G$33+$C63*G$39+$C64*G$45+$C65*G$51+$C60</f>
         <v>64.5522445946282</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>33</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>34</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>35</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="1">
-        <v>5.3</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C61" s="1">
-        <v>1.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
+        <v>34</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>35</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="1">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>36</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
         <v>37</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" s="1">
+      <c r="B65" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="1">
         <v>5.3</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="8"/>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="8"/>
+    <row r="66" spans="2:2">
+      <c r="B66" s="8"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2179,7 +2217,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:G70"/>
+  <dimension ref="A3:G74"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="8.88888888888889" style="1"/>
@@ -2257,902 +2295,955 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:7">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6">
-        <f>IF($C10="identity",D11,IF($C10="sigmoid",1/(1+EXP(-D11)),IF($C10="tanh",(EXP(D11)-EXP(-D11))/(EXP(D11)+EXP(-D11)),IF($C10="softplus",LN(1+EXP(D11)),IF($C10="gaussian",EXP(-POWER(D11,2)),0)))))</f>
-        <v>0.00840906806596298</v>
-      </c>
-      <c r="E10" s="6">
-        <f>IF($C10="identity",E11,IF($C10="sigmoid",1/(1+EXP(-E11)),IF($C10="tanh",(EXP(E11)-EXP(-E11))/(EXP(E11)+EXP(-E11)),IF($C10="softplus",LN(1+EXP(E11)),IF($C10="gaussian",EXP(-POWER(E11,2)),0)))))</f>
-        <v>0.00654166762096193</v>
-      </c>
-      <c r="F10" s="6">
-        <f>IF($C10="identity",F11,IF($C10="sigmoid",1/(1+EXP(-F11)),IF($C10="tanh",(EXP(F11)-EXP(-F11))/(EXP(F11)+EXP(-F11)),IF($C10="softplus",LN(1+EXP(F11)),IF($C10="gaussian",EXP(-POWER(F11,2)),0)))))</f>
-        <v>0.00669285092428486</v>
-      </c>
-      <c r="G10" s="6">
-        <f>IF($C10="identity",G11,IF($C10="sigmoid",1/(1+EXP(-G11)),IF($C10="tanh",(EXP(G11)-EXP(-G11))/(EXP(G11)+EXP(-G11)),IF($C10="softplus",LN(1+EXP(G11)),IF($C10="gaussian",EXP(-POWER(G11,2)),0)))))</f>
-        <v>0.00532501768574217</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1">
-        <v>-5</v>
-      </c>
-      <c r="D11" s="2">
-        <f>$C12*D$4+$C11</f>
-        <v>-4.77</v>
-      </c>
-      <c r="E11" s="2">
-        <f>$C12*E$4+$C11</f>
-        <v>-5.023</v>
-      </c>
-      <c r="F11" s="2">
-        <f>$C12*F$4+$C11</f>
-        <v>-5</v>
-      </c>
-      <c r="G11" s="2">
-        <f>$C12*G$4+$C11</f>
-        <v>-5.23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0.23</v>
+      <c r="D9" s="2">
+        <f t="shared" ref="D9:G9" si="0">D60</f>
+        <v>-53.3715221646747</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>107.161734817953</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>-35.9621820746993</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>-57.6998301798879</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" ref="D10:G10" si="1">D68</f>
+        <v>146.408201315051</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="1"/>
+        <v>179.392092569437</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>347.189125665364</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="1"/>
+        <v>97.2893002888476</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D14" s="6">
         <f>IF($C14="identity",D15,IF($C14="sigmoid",1/(1+EXP(-D15)),IF($C14="tanh",(EXP(D15)-EXP(-D15))/(EXP(D15)+EXP(-D15)),IF($C14="softplus",LN(1+EXP(D15)),IF($C14="gaussian",EXP(-POWER(D15,2)),0)))))</f>
-        <v>-1</v>
+        <v>0.00840906806596298</v>
       </c>
       <c r="E14" s="6">
         <f>IF($C14="identity",E15,IF($C14="sigmoid",1/(1+EXP(-E15)),IF($C14="tanh",(EXP(E15)-EXP(-E15))/(EXP(E15)+EXP(-E15)),IF($C14="softplus",LN(1+EXP(E15)),IF($C14="gaussian",EXP(-POWER(E15,2)),0)))))</f>
-        <v>0.859126538214366</v>
+        <v>0.00654166762096193</v>
       </c>
       <c r="F14" s="6">
         <f>IF($C14="identity",F15,IF($C14="sigmoid",1/(1+EXP(-F15)),IF($C14="tanh",(EXP(F15)-EXP(-F15))/(EXP(F15)+EXP(-F15)),IF($C14="softplus",LN(1+EXP(F15)),IF($C14="gaussian",EXP(-POWER(F15,2)),0)))))</f>
-        <v>-1</v>
+        <v>0.00669285092428486</v>
       </c>
       <c r="G14" s="6">
         <f>IF($C14="identity",G15,IF($C14="sigmoid",1/(1+EXP(-G15)),IF($C14="tanh",(EXP(G15)-EXP(-G15))/(EXP(G15)+EXP(-G15)),IF($C14="softplus",LN(1+EXP(G15)),IF($C14="gaussian",EXP(-POWER(G15,2)),0)))))</f>
-        <v>-0.99999999999315</v>
+        <v>0.00532501768574217</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1">
-        <v>0.6</v>
+        <v>-5</v>
       </c>
       <c r="D15" s="2">
-        <f>$C16*D$5+$C15</f>
-        <v>-68.4</v>
+        <f>$C16*D$4+$C15</f>
+        <v>-4.77</v>
       </c>
       <c r="E15" s="2">
-        <f>$C16*E$5+$C15</f>
-        <v>1.29</v>
+        <f>$C16*E$4+$C15</f>
+        <v>-5.023</v>
       </c>
       <c r="F15" s="2">
-        <f>$C16*F$5+$C15</f>
-        <v>-40.8</v>
+        <f>$C16*F$4+$C15</f>
+        <v>-5</v>
       </c>
       <c r="G15" s="2">
-        <f>$C16*G$5+$C15</f>
-        <v>-13.2</v>
+        <f>$C16*G$4+$C15</f>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1">
-        <v>13.8</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
         <f>IF($C18="identity",D19,IF($C18="sigmoid",1/(1+EXP(-D19)),IF($C18="tanh",(EXP(D19)-EXP(-D19))/(EXP(D19)+EXP(-D19)),IF($C18="softplus",LN(1+EXP(D19)),IF($C18="gaussian",EXP(-POWER(D19,2)),0)))))</f>
-        <v>1.06022557001708</v>
+        <v>-1</v>
       </c>
       <c r="E18" s="6">
         <f>IF($C18="identity",E19,IF($C18="sigmoid",1/(1+EXP(-E19)),IF($C18="tanh",(EXP(E19)-EXP(-E19))/(EXP(E19)+EXP(-E19)),IF($C18="softplus",LN(1+EXP(E19)),IF($C18="gaussian",EXP(-POWER(E19,2)),0)))))</f>
-        <v>0.0593777457537416</v>
+        <v>0.859126538214366</v>
       </c>
       <c r="F18" s="6">
         <f>IF($C18="identity",F19,IF($C18="sigmoid",1/(1+EXP(-F19)),IF($C18="tanh",(EXP(F19)-EXP(-F19))/(EXP(F19)+EXP(-F19)),IF($C18="softplus",LN(1+EXP(F19)),IF($C18="gaussian",EXP(-POWER(F19,2)),0)))))</f>
-        <v>5.08620064521996</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="6">
         <f>IF($C18="identity",G19,IF($C18="sigmoid",1/(1+EXP(-G19)),IF($C18="tanh",(EXP(G19)-EXP(-G19))/(EXP(G19)+EXP(-G19)),IF($C18="softplus",LN(1+EXP(G19)),IF($C18="gaussian",EXP(-POWER(G19,2)),0)))))</f>
-        <v>0.0759108600655253</v>
+        <v>-0.99999999999315</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D19" s="2">
-        <f>$C20*D$6+$C19</f>
-        <v>0.635</v>
+        <f>$C20*D$5+$C19</f>
+        <v>-68.4</v>
       </c>
       <c r="E19" s="2">
-        <f>$C20*E$6+$C19</f>
-        <v>-2.794</v>
+        <f>$C20*E$5+$C19</f>
+        <v>1.29</v>
       </c>
       <c r="F19" s="2">
-        <f>$C20*F$6+$C19</f>
-        <v>5.08</v>
+        <f>$C20*F$5+$C19</f>
+        <v>-40.8</v>
       </c>
       <c r="G19" s="2">
-        <f>$C20*G$6+$C19</f>
-        <v>-2.54</v>
+        <f>$C20*G$5+$C19</f>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="6">
+        <f>IF($C22="identity",D23,IF($C22="sigmoid",1/(1+EXP(-D23)),IF($C22="tanh",(EXP(D23)-EXP(-D23))/(EXP(D23)+EXP(-D23)),IF($C22="softplus",LN(1+EXP(D23)),IF($C22="gaussian",EXP(-POWER(D23,2)),0)))))</f>
+        <v>1.06022557001708</v>
+      </c>
+      <c r="E22" s="6">
+        <f>IF($C22="identity",E23,IF($C22="sigmoid",1/(1+EXP(-E23)),IF($C22="tanh",(EXP(E23)-EXP(-E23))/(EXP(E23)+EXP(-E23)),IF($C22="softplus",LN(1+EXP(E23)),IF($C22="gaussian",EXP(-POWER(E23,2)),0)))))</f>
+        <v>0.0593777457537416</v>
+      </c>
+      <c r="F22" s="6">
+        <f>IF($C22="identity",F23,IF($C22="sigmoid",1/(1+EXP(-F23)),IF($C22="tanh",(EXP(F23)-EXP(-F23))/(EXP(F23)+EXP(-F23)),IF($C22="softplus",LN(1+EXP(F23)),IF($C22="gaussian",EXP(-POWER(F23,2)),0)))))</f>
+        <v>5.08620064521996</v>
+      </c>
+      <c r="G22" s="6">
+        <f>IF($C22="identity",G23,IF($C22="sigmoid",1/(1+EXP(-G23)),IF($C22="tanh",(EXP(G23)-EXP(-G23))/(EXP(G23)+EXP(-G23)),IF($C22="softplus",LN(1+EXP(G23)),IF($C22="gaussian",EXP(-POWER(G23,2)),0)))))</f>
+        <v>0.0759108600655253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <f>$C24*D$6+$C23</f>
+        <v>0.635</v>
+      </c>
+      <c r="E23" s="2">
+        <f>$C24*E$6+$C23</f>
+        <v>-2.794</v>
+      </c>
+      <c r="F23" s="2">
+        <f>$C24*F$6+$C23</f>
+        <v>5.08</v>
+      </c>
+      <c r="G23" s="2">
+        <f>$C24*G$6+$C23</f>
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>8</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="8"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="1">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="8"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="3" t="s">
+      <c r="C28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="6">
+        <f>IF($C28="identity",D29,IF($C28="sigmoid",1/(1+EXP(-D29)),IF($C28="tanh",(EXP(D29)-EXP(-D29))/(EXP(D29)+EXP(-D29)),IF($C28="softplus",LN(1+EXP(D29)),IF($C28="gaussian",EXP(-POWER(D29,2)),0)))))</f>
+        <v>-0.578870393254329</v>
+      </c>
+      <c r="E28" s="6">
+        <f>IF($C28="identity",E29,IF($C28="sigmoid",1/(1+EXP(-E29)),IF($C28="tanh",(EXP(E29)-EXP(-E29))/(EXP(E29)+EXP(-E29)),IF($C28="softplus",LN(1+EXP(E29)),IF($C28="gaussian",EXP(-POWER(E29,2)),0)))))</f>
+        <v>-3.65284151809511</v>
+      </c>
+      <c r="F28" s="6">
+        <f>IF($C28="identity",F29,IF($C28="sigmoid",1/(1+EXP(-F29)),IF($C28="tanh",(EXP(F29)-EXP(-F29))/(EXP(F29)+EXP(-F29)),IF($C28="softplus",LN(1+EXP(F29)),IF($C28="gaussian",EXP(-POWER(F29,2)),0)))))</f>
+        <v>20.7584027753784</v>
+      </c>
+      <c r="G28" s="6">
+        <f>IF($C28="identity",G29,IF($C28="sigmoid",1/(1+EXP(-G29)),IF($C28="tanh",(EXP(G29)-EXP(-G29))/(EXP(G29)+EXP(-G29)),IF($C28="softplus",LN(1+EXP(G29)),IF($C28="gaussian",EXP(-POWER(G29,2)),0)))))</f>
+        <v>-5.79644768757678</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="1">
+        <v>-5</v>
+      </c>
+      <c r="D29" s="2">
+        <f>$C30*D$14+$C31*D$18+$C32*D$22+$C29</f>
+        <v>-0.578870393254329</v>
+      </c>
+      <c r="E29" s="2">
+        <f>$C30*E$14+$C31*E$18+$C32*E$22+$C29</f>
+        <v>-3.65284151809511</v>
+      </c>
+      <c r="F29" s="2">
+        <f>$C30*F$14+$C31*F$18+$C32*F$22+$C29</f>
+        <v>20.7584027753784</v>
+      </c>
+      <c r="G29" s="2">
+        <f>$C30*G$14+$C31*G$18+$C32*G$22+$C29</f>
+        <v>-5.79644768757678</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6">
-        <f>IF($C24="identity",D25,IF($C24="sigmoid",1/(1+EXP(-D25)),IF($C24="tanh",(EXP(D25)-EXP(-D25))/(EXP(D25)+EXP(-D25)),IF($C24="softplus",LN(1+EXP(D25)),IF($C24="gaussian",EXP(-POWER(D25,2)),0)))))</f>
-        <v>-0.578870393254329</v>
-      </c>
-      <c r="E24" s="6">
-        <f>IF($C24="identity",E25,IF($C24="sigmoid",1/(1+EXP(-E25)),IF($C24="tanh",(EXP(E25)-EXP(-E25))/(EXP(E25)+EXP(-E25)),IF($C24="softplus",LN(1+EXP(E25)),IF($C24="gaussian",EXP(-POWER(E25,2)),0)))))</f>
-        <v>-3.65284151809511</v>
-      </c>
-      <c r="F24" s="6">
-        <f>IF($C24="identity",F25,IF($C24="sigmoid",1/(1+EXP(-F25)),IF($C24="tanh",(EXP(F25)-EXP(-F25))/(EXP(F25)+EXP(-F25)),IF($C24="softplus",LN(1+EXP(F25)),IF($C24="gaussian",EXP(-POWER(F25,2)),0)))))</f>
-        <v>20.7584027753784</v>
-      </c>
-      <c r="G24" s="6">
-        <f>IF($C24="identity",G25,IF($C24="sigmoid",1/(1+EXP(-G25)),IF($C24="tanh",(EXP(G25)-EXP(-G25))/(EXP(G25)+EXP(-G25)),IF($C24="softplus",LN(1+EXP(G25)),IF($C24="gaussian",EXP(-POWER(G25,2)),0)))))</f>
-        <v>-5.79644768757678</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>9</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="C30" s="1">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>11</v>
       </c>
-      <c r="C25" s="1">
-        <v>-5</v>
-      </c>
-      <c r="D25" s="2">
-        <f>$C26*D$10+$C27*D$14+$C28*D$18+$C25</f>
-        <v>-0.578870393254329</v>
-      </c>
-      <c r="E25" s="2">
-        <f>$C26*E$10+$C27*E$14+$C28*E$18+$C25</f>
-        <v>-3.65284151809511</v>
-      </c>
-      <c r="F25" s="2">
-        <f>$C26*F$10+$C27*F$14+$C28*F$18+$C25</f>
-        <v>20.7584027753784</v>
-      </c>
-      <c r="G25" s="2">
-        <f>$C26*G$10+$C27*G$14+$C28*G$18+$C25</f>
-        <v>-5.79644768757678</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>10</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>11</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="1">
+      <c r="B31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1">
         <v>1.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>12</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="6">
-        <f>IF($C30="identity",D31,IF($C30="sigmoid",1/(1+EXP(-D31)),IF($C30="tanh",(EXP(D31)-EXP(-D31))/(EXP(D31)+EXP(-D31)),IF($C30="softplus",LN(1+EXP(D31)),IF($C30="gaussian",EXP(-POWER(D31,2)),0)))))</f>
-        <v>8.83943806726029</v>
-      </c>
-      <c r="E30" s="6">
-        <f>IF($C30="identity",E31,IF($C30="sigmoid",1/(1+EXP(-E31)),IF($C30="tanh",(EXP(E31)-EXP(-E31))/(EXP(E31)+EXP(-E31)),IF($C30="softplus",LN(1+EXP(E31)),IF($C30="gaussian",EXP(-POWER(E31,2)),0)))))</f>
-        <v>1.28837851175534</v>
-      </c>
-      <c r="F30" s="6">
-        <f>IF($C30="identity",F31,IF($C30="sigmoid",1/(1+EXP(-F31)),IF($C30="tanh",(EXP(F31)-EXP(-F31))/(EXP(F31)+EXP(-F31)),IF($C30="softplus",LN(1+EXP(F31)),IF($C30="gaussian",EXP(-POWER(F31,2)),0)))))</f>
-        <v>4.81353164074306</v>
-      </c>
-      <c r="G30" s="6">
-        <f>IF($C30="identity",G31,IF($C30="sigmoid",1/(1+EXP(-G31)),IF($C30="tanh",(EXP(G31)-EXP(-G31))/(EXP(G31)+EXP(-G31)),IF($C30="softplus",LN(1+EXP(G31)),IF($C30="gaussian",EXP(-POWER(G31,2)),0)))))</f>
-        <v>9.82387613919554</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>13</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="D31" s="2">
-        <f>$C32*D$10+$C33*D$14+$C34*D$18+$C31</f>
-        <v>8.83943806726029</v>
-      </c>
-      <c r="E31" s="2">
-        <f>$C32*E$10+$C33*E$14+$C34*E$18+$C31</f>
-        <v>1.28837851175534</v>
-      </c>
-      <c r="F31" s="2">
-        <f>$C32*F$10+$C33*F$14+$C34*F$18+$C31</f>
-        <v>4.81353164074306</v>
-      </c>
-      <c r="G31" s="2">
-        <f>$C32*G$10+$C33*G$14+$C34*G$18+$C31</f>
-        <v>9.82387613919554</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
+        <v>12</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="1">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6">
+        <f>IF($C34="identity",D35,IF($C34="sigmoid",1/(1+EXP(-D35)),IF($C34="tanh",(EXP(D35)-EXP(-D35))/(EXP(D35)+EXP(-D35)),IF($C34="softplus",LN(1+EXP(D35)),IF($C34="gaussian",EXP(-POWER(D35,2)),0)))))</f>
+        <v>8.83943806726029</v>
+      </c>
+      <c r="E34" s="6">
+        <f>IF($C34="identity",E35,IF($C34="sigmoid",1/(1+EXP(-E35)),IF($C34="tanh",(EXP(E35)-EXP(-E35))/(EXP(E35)+EXP(-E35)),IF($C34="softplus",LN(1+EXP(E35)),IF($C34="gaussian",EXP(-POWER(E35,2)),0)))))</f>
+        <v>1.28837851175534</v>
+      </c>
+      <c r="F34" s="6">
+        <f>IF($C34="identity",F35,IF($C34="sigmoid",1/(1+EXP(-F35)),IF($C34="tanh",(EXP(F35)-EXP(-F35))/(EXP(F35)+EXP(-F35)),IF($C34="softplus",LN(1+EXP(F35)),IF($C34="gaussian",EXP(-POWER(F35,2)),0)))))</f>
+        <v>4.81353164074306</v>
+      </c>
+      <c r="G34" s="6">
+        <f>IF($C34="identity",G35,IF($C34="sigmoid",1/(1+EXP(-G35)),IF($C34="tanh",(EXP(G35)-EXP(-G35))/(EXP(G35)+EXP(-G35)),IF($C34="softplus",LN(1+EXP(G35)),IF($C34="gaussian",EXP(-POWER(G35,2)),0)))))</f>
+        <v>9.82387613919554</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>13</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1">
+      <c r="C35" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="D35" s="2">
+        <f>$C36*D$14+$C37*D$18+$C38*D$22+$C35</f>
+        <v>8.83943806726029</v>
+      </c>
+      <c r="E35" s="2">
+        <f>$C36*E$14+$C37*E$18+$C38*E$22+$C35</f>
+        <v>1.28837851175534</v>
+      </c>
+      <c r="F35" s="2">
+        <f>$C36*F$14+$C37*F$18+$C38*F$22+$C35</f>
+        <v>4.81353164074306</v>
+      </c>
+      <c r="G35" s="2">
+        <f>$C36*G$14+$C37*G$18+$C38*G$22+$C35</f>
+        <v>9.82387613919554</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>14</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
         <v>-0.04</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>15</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="1">
+      <c r="B37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1">
         <v>-4.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34">
-        <v>16</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="6">
-        <f>IF($C36="identity",D37,IF($C36="sigmoid",1/(1+EXP(-D37)),IF($C36="tanh",(EXP(D37)-EXP(-D37))/(EXP(D37)+EXP(-D37)),IF($C36="softplus",LN(1+EXP(D37)),IF($C36="gaussian",EXP(-POWER(D37,2)),0)))))</f>
-        <v>-8.51847629907172</v>
-      </c>
-      <c r="E36" s="6">
-        <f>IF($C36="identity",E37,IF($C36="sigmoid",1/(1+EXP(-E37)),IF($C36="tanh",(EXP(E37)-EXP(-E37))/(EXP(E37)+EXP(-E37)),IF($C36="softplus",LN(1+EXP(E37)),IF($C36="gaussian",EXP(-POWER(E37,2)),0)))))</f>
-        <v>8.62433704465963</v>
-      </c>
-      <c r="F36" s="6">
-        <f>IF($C36="identity",F37,IF($C36="sigmoid",1/(1+EXP(-F37)),IF($C36="tanh",(EXP(F37)-EXP(-F37))/(EXP(F37)+EXP(-F37)),IF($C36="softplus",LN(1+EXP(F37)),IF($C36="gaussian",EXP(-POWER(F37,2)),0)))))</f>
-        <v>-10.937665400191</v>
-      </c>
-      <c r="G36" s="6">
-        <f>IF($C36="identity",G37,IF($C36="sigmoid",1/(1+EXP(-G37)),IF($C36="tanh",(EXP(G37)-EXP(-G37))/(EXP(G37)+EXP(-G37)),IF($C36="softplus",LN(1+EXP(G37)),IF($C36="gaussian",EXP(-POWER(G37,2)),0)))))</f>
-        <v>-7.9343639788383</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>17</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="2">
-        <f>$C38*D$10+$C39*D$14+$C40*D$18+$C37</f>
-        <v>-8.51847629907172</v>
-      </c>
-      <c r="E37" s="2">
-        <f>$C38*E$10+$C39*E$14+$C40*E$18+$C37</f>
-        <v>8.62433704465963</v>
-      </c>
-      <c r="F37" s="2">
-        <f>$C38*F$10+$C39*F$14+$C40*F$18+$C37</f>
-        <v>-10.937665400191</v>
-      </c>
-      <c r="G37" s="2">
-        <f>$C38*G$10+$C39*G$14+$C40*G$18+$C37</f>
-        <v>-7.9343639788383</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
+        <v>16</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="6">
+        <f>IF($C40="identity",D41,IF($C40="sigmoid",1/(1+EXP(-D41)),IF($C40="tanh",(EXP(D41)-EXP(-D41))/(EXP(D41)+EXP(-D41)),IF($C40="softplus",LN(1+EXP(D41)),IF($C40="gaussian",EXP(-POWER(D41,2)),0)))))</f>
+        <v>-8.51847629907172</v>
+      </c>
+      <c r="E40" s="6">
+        <f>IF($C40="identity",E41,IF($C40="sigmoid",1/(1+EXP(-E41)),IF($C40="tanh",(EXP(E41)-EXP(-E41))/(EXP(E41)+EXP(-E41)),IF($C40="softplus",LN(1+EXP(E41)),IF($C40="gaussian",EXP(-POWER(E41,2)),0)))))</f>
+        <v>8.62433704465963</v>
+      </c>
+      <c r="F40" s="6">
+        <f>IF($C40="identity",F41,IF($C40="sigmoid",1/(1+EXP(-F41)),IF($C40="tanh",(EXP(F41)-EXP(-F41))/(EXP(F41)+EXP(-F41)),IF($C40="softplus",LN(1+EXP(F41)),IF($C40="gaussian",EXP(-POWER(F41,2)),0)))))</f>
+        <v>-10.937665400191</v>
+      </c>
+      <c r="G40" s="6">
+        <f>IF($C40="identity",G41,IF($C40="sigmoid",1/(1+EXP(-G41)),IF($C40="tanh",(EXP(G41)-EXP(-G41))/(EXP(G41)+EXP(-G41)),IF($C40="softplus",LN(1+EXP(G41)),IF($C40="gaussian",EXP(-POWER(G41,2)),0)))))</f>
+        <v>-7.9343639788383</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>17</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <f>$C42*D$14+$C43*D$18+$C44*D$22+$C41</f>
+        <v>-8.51847629907172</v>
+      </c>
+      <c r="E41" s="2">
+        <f>$C42*E$14+$C43*E$18+$C44*E$22+$C41</f>
+        <v>8.62433704465963</v>
+      </c>
+      <c r="F41" s="2">
+        <f>$C42*F$14+$C43*F$18+$C44*F$22+$C41</f>
+        <v>-10.937665400191</v>
+      </c>
+      <c r="G41" s="2">
+        <f>$C42*G$14+$C43*G$18+$C44*G$22+$C41</f>
+        <v>-7.9343639788383</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>18</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="1">
+      <c r="B42" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="1">
         <v>2.1</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>19</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="B43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1">
         <v>8.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40">
-        <v>20</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="1">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="6">
-        <f>IF($C42="identity",D43,IF($C42="sigmoid",1/(1+EXP(-D43)),IF($C42="tanh",(EXP(D43)-EXP(-D43))/(EXP(D43)+EXP(-D43)),IF($C42="softplus",LN(1+EXP(D43)),IF($C42="gaussian",EXP(-POWER(D43,2)),0)))))</f>
-        <v>0.0518908577811719</v>
-      </c>
-      <c r="E42" s="6">
-        <f>IF($C42="identity",E43,IF($C42="sigmoid",1/(1+EXP(-E43)),IF($C42="tanh",(EXP(E43)-EXP(-E43))/(EXP(E43)+EXP(-E43)),IF($C42="softplus",LN(1+EXP(E43)),IF($C42="gaussian",EXP(-POWER(E43,2)),0)))))</f>
-        <v>0.0590292798131092</v>
-      </c>
-      <c r="F42" s="6">
-        <f>IF($C42="identity",F43,IF($C42="sigmoid",1/(1+EXP(-F43)),IF($C42="tanh",(EXP(F43)-EXP(-F43))/(EXP(F43)+EXP(-F43)),IF($C42="softplus",LN(1+EXP(F43)),IF($C42="gaussian",EXP(-POWER(F43,2)),0)))))</f>
-        <v>0.172652947865842</v>
-      </c>
-      <c r="G42" s="6">
-        <f>IF($C42="identity",G43,IF($C42="sigmoid",1/(1+EXP(-G43)),IF($C42="tanh",(EXP(G43)-EXP(-G43))/(EXP(G43)+EXP(-G43)),IF($C42="softplus",LN(1+EXP(G43)),IF($C42="gaussian",EXP(-POWER(G43,2)),0)))))</f>
-        <v>0.0223305759789602</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="D43" s="2">
-        <f>$C44*D$10+$C45*D$14+$C46*D$18+$C43</f>
-        <v>0.0518908577811719</v>
-      </c>
-      <c r="E43" s="2">
-        <f>$C44*E$10+$C45*E$14+$C46*E$18+$C43</f>
-        <v>0.0590292798131092</v>
-      </c>
-      <c r="F43" s="2">
-        <f>$C44*F$10+$C45*F$14+$C46*F$18+$C43</f>
-        <v>0.172652947865842</v>
-      </c>
-      <c r="G43" s="2">
-        <f>$C44*G$10+$C45*G$14+$C46*G$18+$C43</f>
-        <v>0.0223305759789602</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
+        <v>20</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="1">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="6">
+        <f>IF($C46="identity",D47,IF($C46="sigmoid",1/(1+EXP(-D47)),IF($C46="tanh",(EXP(D47)-EXP(-D47))/(EXP(D47)+EXP(-D47)),IF($C46="softplus",LN(1+EXP(D47)),IF($C46="gaussian",EXP(-POWER(D47,2)),0)))))</f>
+        <v>0.0518908577811719</v>
+      </c>
+      <c r="E46" s="6">
+        <f>IF($C46="identity",E47,IF($C46="sigmoid",1/(1+EXP(-E47)),IF($C46="tanh",(EXP(E47)-EXP(-E47))/(EXP(E47)+EXP(-E47)),IF($C46="softplus",LN(1+EXP(E47)),IF($C46="gaussian",EXP(-POWER(E47,2)),0)))))</f>
+        <v>0.0590292798131092</v>
+      </c>
+      <c r="F46" s="6">
+        <f>IF($C46="identity",F47,IF($C46="sigmoid",1/(1+EXP(-F47)),IF($C46="tanh",(EXP(F47)-EXP(-F47))/(EXP(F47)+EXP(-F47)),IF($C46="softplus",LN(1+EXP(F47)),IF($C46="gaussian",EXP(-POWER(F47,2)),0)))))</f>
+        <v>0.172652947865842</v>
+      </c>
+      <c r="G46" s="6">
+        <f>IF($C46="identity",G47,IF($C46="sigmoid",1/(1+EXP(-G47)),IF($C46="tanh",(EXP(G47)-EXP(-G47))/(EXP(G47)+EXP(-G47)),IF($C46="softplus",LN(1+EXP(G47)),IF($C46="gaussian",EXP(-POWER(G47,2)),0)))))</f>
+        <v>0.0223305759789602</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="D47" s="2">
+        <f>$C48*D$14+$C49*D$18+$C50*D$22+$C47</f>
+        <v>0.0518908577811719</v>
+      </c>
+      <c r="E47" s="2">
+        <f>$C48*E$14+$C49*E$18+$C50*E$22+$C47</f>
+        <v>0.0590292798131092</v>
+      </c>
+      <c r="F47" s="2">
+        <f>$C48*F$14+$C49*F$18+$C50*F$22+$C47</f>
+        <v>0.172652947865842</v>
+      </c>
+      <c r="G47" s="2">
+        <f>$C48*G$14+$C49*G$18+$C50*G$22+$C47</f>
+        <v>0.0223305759789602</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>22</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="1">
+      <c r="B48" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="1">
         <v>0.01</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>23</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="1">
+      <c r="B49" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="1">
         <v>0.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46">
-        <v>24</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="6">
-        <f>IF($C48="identity",D49,IF($C48="sigmoid",1/(1+EXP(-D49)),IF($C48="tanh",(EXP(D49)-EXP(-D49))/(EXP(D49)+EXP(-D49)),IF($C48="softplus",LN(1+EXP(D49)),IF($C48="gaussian",EXP(-POWER(D49,2)),0)))))</f>
-        <v>35.0980511661378</v>
-      </c>
-      <c r="E48" s="6">
-        <f>IF($C48="identity",E49,IF($C48="sigmoid",1/(1+EXP(-E49)),IF($C48="tanh",(EXP(E49)-EXP(-E49))/(EXP(E49)+EXP(-E49)),IF($C48="softplus",LN(1+EXP(E49)),IF($C48="gaussian",EXP(-POWER(E49,2)),0)))))</f>
-        <v>26.0200698928341</v>
-      </c>
-      <c r="F48" s="6">
-        <f>IF($C48="identity",F49,IF($C48="sigmoid",1/(1+EXP(-F49)),IF($C48="tanh",(EXP(F49)-EXP(-F49))/(EXP(F49)+EXP(-F49)),IF($C48="softplus",LN(1+EXP(F49)),IF($C48="gaussian",EXP(-POWER(F49,2)),0)))))</f>
-        <v>75.3586600267375</v>
-      </c>
-      <c r="G48" s="6">
-        <f>IF($C48="identity",G49,IF($C48="sigmoid",1/(1+EXP(-G49)),IF($C48="tanh",(EXP(G49)-EXP(-G49))/(EXP(G49)+EXP(-G49)),IF($C48="softplus",LN(1+EXP(G49)),IF($C48="gaussian",EXP(-POWER(G49,2)),0)))))</f>
-        <v>25.2564460918158</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>25</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="1">
-        <v>25</v>
-      </c>
-      <c r="D49" s="2">
-        <f>$C50*D$10+$C51*D$14+$C52*D$18+$C49</f>
-        <v>35.0980511661378</v>
-      </c>
-      <c r="E49" s="2">
-        <f>$C50*E$10+$C51*E$14+$C52*E$18+$C49</f>
-        <v>26.0200698928341</v>
-      </c>
-      <c r="F49" s="2">
-        <f>$C50*F$10+$C51*F$14+$C52*F$18+$C49</f>
-        <v>75.3586600267375</v>
-      </c>
-      <c r="G49" s="2">
-        <f>$C50*G$10+$C51*G$14+$C52*G$18+$C49</f>
-        <v>25.2564460918158</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
+        <v>24</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="1">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
+      <c r="B52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="6">
+        <f>IF($C52="identity",D53,IF($C52="sigmoid",1/(1+EXP(-D53)),IF($C52="tanh",(EXP(D53)-EXP(-D53))/(EXP(D53)+EXP(-D53)),IF($C52="softplus",LN(1+EXP(D53)),IF($C52="gaussian",EXP(-POWER(D53,2)),0)))))</f>
+        <v>35.0980511661378</v>
+      </c>
+      <c r="E52" s="6">
+        <f>IF($C52="identity",E53,IF($C52="sigmoid",1/(1+EXP(-E53)),IF($C52="tanh",(EXP(E53)-EXP(-E53))/(EXP(E53)+EXP(-E53)),IF($C52="softplus",LN(1+EXP(E53)),IF($C52="gaussian",EXP(-POWER(E53,2)),0)))))</f>
+        <v>26.0200698928341</v>
+      </c>
+      <c r="F52" s="6">
+        <f>IF($C52="identity",F53,IF($C52="sigmoid",1/(1+EXP(-F53)),IF($C52="tanh",(EXP(F53)-EXP(-F53))/(EXP(F53)+EXP(-F53)),IF($C52="softplus",LN(1+EXP(F53)),IF($C52="gaussian",EXP(-POWER(F53,2)),0)))))</f>
+        <v>75.3586600267375</v>
+      </c>
+      <c r="G52" s="6">
+        <f>IF($C52="identity",G53,IF($C52="sigmoid",1/(1+EXP(-G53)),IF($C52="tanh",(EXP(G53)-EXP(-G53))/(EXP(G53)+EXP(-G53)),IF($C52="softplus",LN(1+EXP(G53)),IF($C52="gaussian",EXP(-POWER(G53,2)),0)))))</f>
+        <v>25.2564460918158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>25</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="1">
+        <v>25</v>
+      </c>
+      <c r="D53" s="2">
+        <f>$C54*D$14+$C55*D$18+$C56*D$22+$C53</f>
+        <v>35.0980511661378</v>
+      </c>
+      <c r="E53" s="2">
+        <f>$C54*E$14+$C55*E$18+$C56*E$22+$C53</f>
+        <v>26.0200698928341</v>
+      </c>
+      <c r="F53" s="2">
+        <f>$C54*F$14+$C55*F$18+$C56*F$22+$C53</f>
+        <v>75.3586600267375</v>
+      </c>
+      <c r="G53" s="2">
+        <f>$C54*G$14+$C55*G$18+$C56*G$22+$C53</f>
+        <v>25.2564460918158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>26</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B54" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="1">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>27</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>28</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="8"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>29</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="1">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>27</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>28</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C52" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="8"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56">
-        <v>29</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="6">
-        <f>IF($C56="identity",D57,IF($C56="sigmoid",1/(1+EXP(-D57)),IF($C56="tanh",(EXP(D57)-EXP(-D57))/(EXP(D57)+EXP(-D57)),IF($C56="softplus",LN(1+EXP(D57)),IF($C56="gaussian",EXP(-POWER(D57,2)),0)))))</f>
-        <v>146.408201315051</v>
-      </c>
-      <c r="E56" s="6">
-        <f>IF($C56="identity",E57,IF($C56="sigmoid",1/(1+EXP(-E57)),IF($C56="tanh",(EXP(E57)-EXP(-E57))/(EXP(E57)+EXP(-E57)),IF($C56="softplus",LN(1+EXP(E57)),IF($C56="gaussian",EXP(-POWER(E57,2)),0)))))</f>
-        <v>179.392092569437</v>
-      </c>
-      <c r="F56" s="6">
-        <f>IF($C56="identity",F57,IF($C56="sigmoid",1/(1+EXP(-F57)),IF($C56="tanh",(EXP(F57)-EXP(-F57))/(EXP(F57)+EXP(-F57)),IF($C56="softplus",LN(1+EXP(F57)),IF($C56="gaussian",EXP(-POWER(F57,2)),0)))))</f>
-        <v>347.189125665364</v>
-      </c>
-      <c r="G56" s="6">
-        <f>IF($C56="identity",G57,IF($C56="sigmoid",1/(1+EXP(-G57)),IF($C56="tanh",(EXP(G57)-EXP(-G57))/(EXP(G57)+EXP(-G57)),IF($C56="softplus",LN(1+EXP(G57)),IF($C56="gaussian",EXP(-POWER(G57,2)),0)))))</f>
-        <v>97.2893002888476</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
+      <c r="C60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="6">
+        <f>IF($C60="identity",D61,IF($C60="sigmoid",1/(1+EXP(-D61)),IF($C60="tanh",(EXP(D61)-EXP(-D61))/(EXP(D61)+EXP(-D61)),IF($C60="softplus",LN(1+EXP(D61)),IF($C60="gaussian",EXP(-POWER(D61,2)),0)))))</f>
+        <v>-53.3715221646747</v>
+      </c>
+      <c r="E60" s="6">
+        <f>IF($C60="identity",E61,IF($C60="sigmoid",1/(1+EXP(-E61)),IF($C60="tanh",(EXP(E61)-EXP(-E61))/(EXP(E61)+EXP(-E61)),IF($C60="softplus",LN(1+EXP(E61)),IF($C60="gaussian",EXP(-POWER(E61,2)),0)))))</f>
+        <v>107.161734817953</v>
+      </c>
+      <c r="F60" s="6">
+        <f>IF($C60="identity",F61,IF($C60="sigmoid",1/(1+EXP(-F61)),IF($C60="tanh",(EXP(F61)-EXP(-F61))/(EXP(F61)+EXP(-F61)),IF($C60="softplus",LN(1+EXP(F61)),IF($C60="gaussian",EXP(-POWER(F61,2)),0)))))</f>
+        <v>-35.9621820746993</v>
+      </c>
+      <c r="G60" s="6">
+        <f>IF($C60="identity",G61,IF($C60="sigmoid",1/(1+EXP(-G61)),IF($C60="tanh",(EXP(G61)-EXP(-G61))/(EXP(G61)+EXP(-G61)),IF($C60="softplus",LN(1+EXP(G61)),IF($C60="gaussian",EXP(-POWER(G61,2)),0)))))</f>
+        <v>-57.6998301798879</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
         <v>30</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="1">
+      <c r="B61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="1">
         <v>-5</v>
       </c>
-      <c r="D57" s="2">
-        <f>$C58*D$24+$C59*D$30+$C60*D$36+$C61*D$42+$C62*D$48+$C57</f>
-        <v>146.408201315051</v>
-      </c>
-      <c r="E57" s="2">
-        <f>$C58*E$24+$C59*E$30+$C60*E$36+$C61*E$42+$C62*E$48+$C57</f>
-        <v>179.392092569437</v>
-      </c>
-      <c r="F57" s="2">
-        <f>$C58*F$24+$C59*F$30+$C60*F$36+$C61*F$42+$C62*F$48+$C57</f>
-        <v>347.189125665364</v>
-      </c>
-      <c r="G57" s="2">
-        <f>$C58*G$24+$C59*G$30+$C60*G$36+$C61*G$42+$C62*G$48+$C57</f>
-        <v>97.2893002888476</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>31</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>32</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>33</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
-        <v>34</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1.2</v>
+      <c r="D61" s="2">
+        <f>$C62*D$28+$C63*D$34+$C64*D$40+$C65*D$46+$C66*D$52+$C61</f>
+        <v>-53.3715221646747</v>
+      </c>
+      <c r="E61" s="2">
+        <f>$C62*E$28+$C63*E$34+$C64*E$40+$C65*E$46+$C66*E$52+$C61</f>
+        <v>107.161734817953</v>
+      </c>
+      <c r="F61" s="2">
+        <f>$C62*F$28+$C63*F$34+$C64*F$40+$C65*F$46+$C66*F$52+$C61</f>
+        <v>-35.9621820746993</v>
+      </c>
+      <c r="G61" s="2">
+        <f>$C62*G$28+$C63*G$34+$C64*G$40+$C65*G$46+$C66*G$52+$C61</f>
+        <v>-57.6998301798879</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C62" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="4" t="s">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>32</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>33</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>34</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64">
-        <v>29</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="6">
-        <f>IF($C64="identity",D65,IF($C64="sigmoid",1/(1+EXP(-D65)),IF($C64="tanh",(EXP(D65)-EXP(-D65))/(EXP(D65)+EXP(-D65)),IF($C64="softplus",LN(1+EXP(D65)),IF($C64="gaussian",EXP(-POWER(D65,2)),0)))))</f>
-        <v>146.408201315051</v>
-      </c>
-      <c r="E64" s="6">
-        <f>IF($C64="identity",E65,IF($C64="sigmoid",1/(1+EXP(-E65)),IF($C64="tanh",(EXP(E65)-EXP(-E65))/(EXP(E65)+EXP(-E65)),IF($C64="softplus",LN(1+EXP(E65)),IF($C64="gaussian",EXP(-POWER(E65,2)),0)))))</f>
-        <v>179.392092569437</v>
-      </c>
-      <c r="F64" s="6">
-        <f>IF($C64="identity",F65,IF($C64="sigmoid",1/(1+EXP(-F65)),IF($C64="tanh",(EXP(F65)-EXP(-F65))/(EXP(F65)+EXP(-F65)),IF($C64="softplus",LN(1+EXP(F65)),IF($C64="gaussian",EXP(-POWER(F65,2)),0)))))</f>
-        <v>347.189125665364</v>
-      </c>
-      <c r="G64" s="6">
-        <f>IF($C64="identity",G65,IF($C64="sigmoid",1/(1+EXP(-G65)),IF($C64="tanh",(EXP(G65)-EXP(-G65))/(EXP(G65)+EXP(-G65)),IF($C64="softplus",LN(1+EXP(G65)),IF($C64="gaussian",EXP(-POWER(G65,2)),0)))))</f>
-        <v>97.2893002888476</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65">
-        <v>30</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="C65" s="1">
-        <v>-5</v>
-      </c>
-      <c r="D65" s="2">
-        <f>$C66*D$24+$C67*D$30+$C68*D$36+$C69*D$42+$C70*D$48+$C65</f>
-        <v>146.408201315051</v>
-      </c>
-      <c r="E65" s="2">
-        <f>$C66*E$24+$C67*E$30+$C68*E$36+$C69*E$42+$C70*E$48+$C65</f>
-        <v>179.392092569437</v>
-      </c>
-      <c r="F65" s="2">
-        <f>$C66*F$24+$C67*F$30+$C68*F$36+$C69*F$42+$C70*F$48+$C65</f>
-        <v>347.189125665364</v>
-      </c>
-      <c r="G65" s="2">
-        <f>$C66*G$24+$C67*G$30+$C68*G$36+$C69*G$42+$C70*G$48+$C65</f>
-        <v>97.2893002888476</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>29</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>32</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="1">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>33</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C68" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="C68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="6">
+        <f>IF($C68="identity",D69,IF($C68="sigmoid",1/(1+EXP(-D69)),IF($C68="tanh",(EXP(D69)-EXP(-D69))/(EXP(D69)+EXP(-D69)),IF($C68="softplus",LN(1+EXP(D69)),IF($C68="gaussian",EXP(-POWER(D69,2)),0)))))</f>
+        <v>146.408201315051</v>
+      </c>
+      <c r="E68" s="6">
+        <f>IF($C68="identity",E69,IF($C68="sigmoid",1/(1+EXP(-E69)),IF($C68="tanh",(EXP(E69)-EXP(-E69))/(EXP(E69)+EXP(-E69)),IF($C68="softplus",LN(1+EXP(E69)),IF($C68="gaussian",EXP(-POWER(E69,2)),0)))))</f>
+        <v>179.392092569437</v>
+      </c>
+      <c r="F68" s="6">
+        <f>IF($C68="identity",F69,IF($C68="sigmoid",1/(1+EXP(-F69)),IF($C68="tanh",(EXP(F69)-EXP(-F69))/(EXP(F69)+EXP(-F69)),IF($C68="softplus",LN(1+EXP(F69)),IF($C68="gaussian",EXP(-POWER(F69,2)),0)))))</f>
+        <v>347.189125665364</v>
+      </c>
+      <c r="G68" s="6">
+        <f>IF($C68="identity",G69,IF($C68="sigmoid",1/(1+EXP(-G69)),IF($C68="tanh",(EXP(G69)-EXP(-G69))/(EXP(G69)+EXP(-G69)),IF($C68="softplus",LN(1+EXP(G69)),IF($C68="gaussian",EXP(-POWER(G69,2)),0)))))</f>
+        <v>97.2893002888476</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C69" s="1">
-        <v>1.2</v>
+        <v>-5</v>
+      </c>
+      <c r="D69" s="2">
+        <f>$C70*D$28+$C71*D$34+$C72*D$40+$C73*D$46+$C74*D$52+$C69</f>
+        <v>146.408201315051</v>
+      </c>
+      <c r="E69" s="2">
+        <f>$C70*E$28+$C71*E$34+$C72*E$40+$C73*E$46+$C74*E$52+$C69</f>
+        <v>179.392092569437</v>
+      </c>
+      <c r="F69" s="2">
+        <f>$C70*F$28+$C71*F$34+$C72*F$40+$C73*F$46+$C74*F$52+$C69</f>
+        <v>347.189125665364</v>
+      </c>
+      <c r="G69" s="2">
+        <f>$C70*G$28+$C71*G$34+$C72*G$40+$C73*G$46+$C74*G$52+$C69</f>
+        <v>97.2893002888476</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
+        <v>31</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>32</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>33</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" s="1">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>34</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
         <v>35</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C70" s="1">
+      <c r="B74" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="1">
         <v>5.3</v>
       </c>
     </row>
